--- a/dist/Dashboard_Susut_ULP_Samboja_2026.xlsx
+++ b/dist/Dashboard_Susut_ULP_Samboja_2026.xlsx
@@ -1036,7 +1036,7 @@
     <t>x</t>
   </si>
   <si>
-    <t>PUTUSAN: sisa potensi work plan 1.926.903 kWh vs gap 1.302.223 kWh = 1.48x  -&gt;  TARGET MASIH BISA DICAPAI, syaratnya seluruh program KRITIS dieksekusi penuh sampai Desember.</t>
+    <t>PUTUSAN: sisa potensi work plan 1.926.702 kWh vs gap 1.302.223 kWh = 1.48x  -&gt;  TARGET MASIH BISA DICAPAI, syaratnya seluruh program KRITIS dieksekusi penuh sampai Desember.</t>
   </si>
   <si>
     <t>CATATAN PENTING</t>
@@ -2943,7 +2943,7 @@
                   <c:v>475333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>143974</c:v>
+                  <c:v>143981</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>117690</c:v>
@@ -2955,16 +2955,16 @@
                   <c:v>110894</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>94760</c:v>
+                  <c:v>94875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93682</c:v>
+                  <c:v>93558</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90720</c:v>
+                  <c:v>90510</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>89007</c:v>
+                  <c:v>89008</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>85008</c:v>
@@ -7095,11 +7095,11 @@
       </c>
       <c r="H7" s="17">
         <f>SUM('INPUT REALISASI'!E8:L8)</f>
-        <v>127.2</v>
+        <v>127.21</v>
       </c>
       <c r="I7" s="16">
         <f>IF(G7=0,0,H7/G7*100)</f>
-        <v>106.0</v>
+        <v>106.01</v>
       </c>
       <c r="J7" s="16">
         <f>IF(F7=0,0,H7/F7*100)</f>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="K7" s="17">
         <f>MAX(F7-H7,0)</f>
-        <v>52.8</v>
+        <v>52.79</v>
       </c>
       <c r="L7" s="17">
         <f>K7/4</f>
@@ -7122,12 +7122,12 @@
         <v>0.83</v>
       </c>
       <c r="O7" s="18">
-        <f>H7*950</f>
-        <v>120840</v>
+        <f>H7*950.0</f>
+        <v>120850</v>
       </c>
       <c r="P7" s="18">
-        <f>K7*950</f>
-        <v>50160</v>
+        <f>K7*950.0</f>
+        <v>50150</v>
       </c>
       <c r="Q7" s="29" t="str">
         <f>IF(I7&gt;=100,"TERCAPAI",IF(I7&gt;=90,"WASPADA",IF(I7&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7154,43 +7154,43 @@
         <v>24.5</v>
       </c>
       <c r="G8" s="17">
-        <v>13.23</v>
+        <v>13.25</v>
       </c>
       <c r="H8" s="17">
         <f>SUM('INPUT REALISASI'!E9:L9)</f>
-        <v>9.39</v>
+        <v>9.41</v>
       </c>
       <c r="I8" s="16">
         <f>IF(G8=0,0,H8/G8*100)</f>
-        <v>71.0</v>
+        <v>71.02</v>
       </c>
       <c r="J8" s="16">
         <f>IF(F8=0,0,H8/F8*100)</f>
-        <v>38.34</v>
+        <v>38.41</v>
       </c>
       <c r="K8" s="17">
         <f>MAX(F8-H8,0)</f>
-        <v>15.11</v>
+        <v>15.09</v>
       </c>
       <c r="L8" s="17">
         <f>K8/4</f>
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="M8" s="17">
         <f>H8/8</f>
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N8" s="17">
         <f>IF(M8=0,"-",L8/M8)</f>
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="O8" s="18">
-        <f>H8*6200</f>
-        <v>58238</v>
+        <f>H8*6200.0</f>
+        <v>58342</v>
       </c>
       <c r="P8" s="18">
-        <f>K8*6200</f>
-        <v>93682</v>
+        <f>K8*6200.0</f>
+        <v>93558</v>
       </c>
       <c r="Q8" s="30" t="str">
         <f>IF(I8&gt;=100,"TERCAPAI",IF(I8&gt;=90,"WASPADA",IF(I8&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7221,19 +7221,19 @@
       </c>
       <c r="H9" s="17">
         <f>SUM('INPUT REALISASI'!E10:L10)</f>
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="I9" s="16">
         <f>IF(G9=0,0,H9/G9*100)</f>
-        <v>58.0</v>
+        <v>57.87</v>
       </c>
       <c r="J9" s="16">
         <f>IF(F9=0,0,H9/F9*100)</f>
-        <v>31.32</v>
+        <v>31.25</v>
       </c>
       <c r="K9" s="17">
         <f>MAX(F9-H9,0)</f>
-        <v>8.24</v>
+        <v>8.25</v>
       </c>
       <c r="L9" s="17">
         <f>K9/4</f>
@@ -7245,15 +7245,15 @@
       </c>
       <c r="N9" s="17">
         <f>IF(M9=0,"-",L9/M9)</f>
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="O9" s="18">
-        <f>H9*11500</f>
-        <v>43222</v>
+        <f>H9*11500.0</f>
+        <v>43125</v>
       </c>
       <c r="P9" s="18">
-        <f>K9*11500</f>
-        <v>94760</v>
+        <f>K9*11500.0</f>
+        <v>94875</v>
       </c>
       <c r="Q9" s="30" t="str">
         <f>IF(I9&gt;=100,"TERCAPAI",IF(I9&gt;=90,"WASPADA",IF(I9&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7280,11 +7280,11 @@
         <v>1450</v>
       </c>
       <c r="G10" s="17">
-        <v>966.67</v>
+        <v>966.64</v>
       </c>
       <c r="H10" s="17">
         <f>SUM('INPUT REALISASI'!E11:L11)</f>
-        <v>802.33</v>
+        <v>802.34</v>
       </c>
       <c r="I10" s="16">
         <f>IF(G10=0,0,H10/G10*100)</f>
@@ -7296,11 +7296,11 @@
       </c>
       <c r="K10" s="17">
         <f>MAX(F10-H10,0)</f>
-        <v>647.67</v>
+        <v>647.66</v>
       </c>
       <c r="L10" s="17">
         <f>K10/4</f>
-        <v>161.92</v>
+        <v>161.91</v>
       </c>
       <c r="M10" s="17">
         <f>H10/8</f>
@@ -7311,12 +7311,12 @@
         <v>1.61</v>
       </c>
       <c r="O10" s="18">
-        <f>H10*62</f>
+        <f>H10*62.0</f>
         <v>49745</v>
       </c>
       <c r="P10" s="18">
-        <f>K10*62</f>
-        <v>40156</v>
+        <f>K10*62.0</f>
+        <v>40155</v>
       </c>
       <c r="Q10" s="31" t="str">
         <f>IF(I10&gt;=100,"TERCAPAI",IF(I10&gt;=90,"WASPADA",IF(I10&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7347,19 +7347,19 @@
       </c>
       <c r="H11" s="17">
         <f>SUM('INPUT REALISASI'!E12:L12)</f>
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I11" s="16">
         <f>IF(G11=0,0,H11/G11*100)</f>
-        <v>50.0</v>
+        <v>50.3</v>
       </c>
       <c r="J11" s="16">
         <f>IF(F11=0,0,H11/F11*100)</f>
-        <v>28.0</v>
+        <v>28.17</v>
       </c>
       <c r="K11" s="17">
         <f>MAX(F11-H11,0)</f>
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="L11" s="17">
         <f>K11/4</f>
@@ -7371,15 +7371,15 @@
       </c>
       <c r="N11" s="17">
         <f>IF(M11=0,"-",L11/M11)</f>
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="O11" s="18">
-        <f>H11*21000</f>
-        <v>35280</v>
+        <f>H11*21000.0</f>
+        <v>35490</v>
       </c>
       <c r="P11" s="18">
-        <f>K11*21000</f>
-        <v>90720</v>
+        <f>K11*21000.0</f>
+        <v>90510</v>
       </c>
       <c r="Q11" s="30" t="str">
         <f>IF(I11&gt;=100,"TERCAPAI",IF(I11&gt;=90,"WASPADA",IF(I11&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7410,23 +7410,23 @@
       </c>
       <c r="H12" s="17">
         <f>SUM('INPUT REALISASI'!E13:L13)</f>
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I12" s="16">
         <f>IF(G12=0,0,H12/G12*100)</f>
-        <v>44.0</v>
+        <v>44.2</v>
       </c>
       <c r="J12" s="16">
         <f>IF(F12=0,0,H12/F12*100)</f>
-        <v>24.64</v>
+        <v>24.75</v>
       </c>
       <c r="K12" s="17">
         <f>MAX(F12-H12,0)</f>
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
       <c r="L12" s="17">
         <f>K12/4</f>
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="17">
         <f>H12/8</f>
@@ -7434,15 +7434,15 @@
       </c>
       <c r="N12" s="17">
         <f>IF(M12=0,"-",L12/M12)</f>
-        <v>6.12</v>
+        <v>6.08</v>
       </c>
       <c r="O12" s="18">
-        <f>H12*13800</f>
-        <v>27203</v>
+        <f>H12*13800.0</f>
+        <v>27324</v>
       </c>
       <c r="P12" s="18">
-        <f>K12*13800</f>
-        <v>83214</v>
+        <f>K12*13800.0</f>
+        <v>83076</v>
       </c>
       <c r="Q12" s="30" t="str">
         <f>IF(I12&gt;=100,"TERCAPAI",IF(I12&gt;=90,"WASPADA",IF(I12&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7469,7 +7469,7 @@
         <v>620</v>
       </c>
       <c r="G13" s="17">
-        <v>413.33</v>
+        <v>413.36</v>
       </c>
       <c r="H13" s="17">
         <f>SUM('INPUT REALISASI'!E14:L14)</f>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="I13" s="16">
         <f>IF(G13=0,0,H13/G13*100)</f>
-        <v>95.0</v>
+        <v>94.99</v>
       </c>
       <c r="J13" s="16">
         <f>IF(F13=0,0,H13/F13*100)</f>
@@ -7500,11 +7500,11 @@
         <v>1.16</v>
       </c>
       <c r="O13" s="18">
-        <f>H13*145</f>
+        <f>H13*145.0</f>
         <v>56937</v>
       </c>
       <c r="P13" s="18">
-        <f>K13*145</f>
+        <f>K13*145.0</f>
         <v>32963</v>
       </c>
       <c r="Q13" s="32" t="str">
@@ -7563,11 +7563,11 @@
         <v>3.53</v>
       </c>
       <c r="O14" s="18">
-        <f>H14*1350</f>
-        <v>21979</v>
+        <f>H14*1350.0</f>
+        <v>21978</v>
       </c>
       <c r="P14" s="18">
-        <f>K14*1350</f>
+        <f>K14*1350.0</f>
         <v>38772</v>
       </c>
       <c r="Q14" s="30" t="str">
@@ -7626,11 +7626,11 @@
         <v>0.94</v>
       </c>
       <c r="O15" s="18">
-        <f>H15*310</f>
+        <f>H15*310.0</f>
         <v>50592</v>
       </c>
       <c r="P15" s="18">
-        <f>K15*310</f>
+        <f>K15*310.0</f>
         <v>23808</v>
       </c>
       <c r="Q15" s="29" t="str">
@@ -7658,23 +7658,23 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G16" s="17">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="H16" s="17">
         <f>SUM('INPUT REALISASI'!E17:L17)</f>
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I16" s="16">
         <f>IF(G16=0,0,H16/G16*100)</f>
-        <v>36.0</v>
+        <v>35.64</v>
       </c>
       <c r="J16" s="16">
         <f>IF(F16=0,0,H16/F16*100)</f>
-        <v>20.16</v>
+        <v>20.0</v>
       </c>
       <c r="K16" s="17">
         <f>MAX(F16-H16,0)</f>
-        <v>7.82</v>
+        <v>7.84</v>
       </c>
       <c r="L16" s="17">
         <f>K16/4</f>
@@ -7682,19 +7682,19 @@
       </c>
       <c r="M16" s="17">
         <f>H16/8</f>
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="N16" s="17">
         <f>IF(M16=0,"-",L16/M16)</f>
-        <v>7.92</v>
+        <v>8.0</v>
       </c>
       <c r="O16" s="18">
-        <f>H16*8900</f>
-        <v>17584</v>
+        <f>H16*8900.0</f>
+        <v>17444</v>
       </c>
       <c r="P16" s="18">
-        <f>K16*8900</f>
-        <v>69598</v>
+        <f>K16*8900.0</f>
+        <v>69776</v>
       </c>
       <c r="Q16" s="30" t="str">
         <f>IF(I16&gt;=100,"TERCAPAI",IF(I16&gt;=90,"WASPADA",IF(I16&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="H17" s="17">
         <f>SUM('INPUT REALISASI'!E18:L18)</f>
-        <v>2208.0</v>
+        <v>2207.98</v>
       </c>
       <c r="I17" s="16">
         <f>IF(G17=0,0,H17/G17*100)</f>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="K17" s="17">
         <f>MAX(F17-H17,0)</f>
-        <v>1392.0</v>
+        <v>1392.02</v>
       </c>
       <c r="L17" s="17">
         <f>K17/4</f>
@@ -7752,11 +7752,11 @@
         <v>1.26</v>
       </c>
       <c r="O17" s="18">
-        <f>H17*0</f>
+        <f>H17*0.0</f>
         <v>0</v>
       </c>
       <c r="P17" s="18">
-        <f>K17*0</f>
+        <f>K17*0.0</f>
         <v>0</v>
       </c>
       <c r="Q17" s="32" t="str">
@@ -7784,7 +7784,7 @@
         <v>1150000</v>
       </c>
       <c r="G18" s="17">
-        <v>766666.67</v>
+        <v>766666.64</v>
       </c>
       <c r="H18" s="17">
         <f>SUM('INPUT REALISASI'!E19:L19)</f>
@@ -7847,11 +7847,11 @@
         <v>3400</v>
       </c>
       <c r="G19" s="17">
-        <v>2266.67</v>
+        <v>2266.64</v>
       </c>
       <c r="H19" s="17">
         <f>SUM('INPUT REALISASI'!E20:L20)</f>
-        <v>1677.33</v>
+        <v>1677.32</v>
       </c>
       <c r="I19" s="16">
         <f>IF(G19=0,0,H19/G19*100)</f>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="K19" s="17">
         <f>MAX(F19-H19,0)</f>
-        <v>1722.67</v>
+        <v>1722.68</v>
       </c>
       <c r="L19" s="17">
         <f>K19/4</f>
@@ -7878,11 +7878,11 @@
         <v>2.05</v>
       </c>
       <c r="O19" s="18">
-        <f>H19*0</f>
+        <f>H19*0.0</f>
         <v>0</v>
       </c>
       <c r="P19" s="18">
-        <f>K19*0</f>
+        <f>K19*0.0</f>
         <v>0</v>
       </c>
       <c r="Q19" s="30" t="str">
@@ -7910,7 +7910,7 @@
         <v>2750</v>
       </c>
       <c r="G20" s="17">
-        <v>1833.33</v>
+        <v>1833.36</v>
       </c>
       <c r="H20" s="17">
         <f>SUM('INPUT REALISASI'!E21:L21)</f>
@@ -7941,11 +7941,11 @@
         <v>1.49</v>
       </c>
       <c r="O20" s="18">
-        <f>H20*96</f>
+        <f>H20*96.0</f>
         <v>151360</v>
       </c>
       <c r="P20" s="18">
-        <f>K20*96</f>
+        <f>K20*96.0</f>
         <v>112640</v>
       </c>
       <c r="Q20" s="31" t="str">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="H21" s="17">
         <f>SUM('INPUT REALISASI'!E22:L22)</f>
-        <v>646.38</v>
+        <v>646.37</v>
       </c>
       <c r="I21" s="16">
         <f>IF(G21=0,0,H21/G21*100)</f>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="K21" s="17">
         <f>MAX(F21-H21,0)</f>
-        <v>1253.62</v>
+        <v>1253.63</v>
       </c>
       <c r="L21" s="17">
         <f>K21/4</f>
@@ -8004,12 +8004,12 @@
         <v>3.88</v>
       </c>
       <c r="O21" s="18">
-        <f>H21*71</f>
-        <v>45893</v>
+        <f>H21*71.0</f>
+        <v>45892</v>
       </c>
       <c r="P21" s="18">
-        <f>K21*71</f>
-        <v>89007</v>
+        <f>K21*71.0</f>
+        <v>89008</v>
       </c>
       <c r="Q21" s="30" t="str">
         <f>IF(I21&gt;=100,"TERCAPAI",IF(I21&gt;=90,"WASPADA",IF(I21&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -8067,11 +8067,11 @@
         <v>1.8</v>
       </c>
       <c r="O22" s="18">
-        <f>H22*1480</f>
+        <f>H22*1480.0</f>
         <v>130950</v>
       </c>
       <c r="P22" s="18">
-        <f>K22*1480</f>
+        <f>K22*1480.0</f>
         <v>117690</v>
       </c>
       <c r="Q22" s="31" t="str">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H23" s="17">
         <f>SUM('INPUT REALISASI'!E24:L24)</f>
-        <v>1104.0</v>
+        <v>1104.01</v>
       </c>
       <c r="I23" s="16">
         <f>IF(G23=0,0,H23/G23*100)</f>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="K23" s="17">
         <f>MAX(F23-H23,0)</f>
-        <v>1296.0</v>
+        <v>1295.99</v>
       </c>
       <c r="L23" s="17">
         <f>K23/4</f>
@@ -8130,12 +8130,12 @@
         <v>2.35</v>
       </c>
       <c r="O23" s="18">
-        <f>H23*58</f>
-        <v>64032</v>
+        <f>H23*58.0</f>
+        <v>64033</v>
       </c>
       <c r="P23" s="18">
-        <f>K23*58</f>
-        <v>75168</v>
+        <f>K23*58.0</f>
+        <v>75167</v>
       </c>
       <c r="Q23" s="30" t="str">
         <f>IF(I23&gt;=100,"TERCAPAI",IF(I23&gt;=90,"WASPADA",IF(I23&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H24" s="17">
         <f>SUM('INPUT REALISASI'!E25:L25)</f>
-        <v>2268.0</v>
+        <v>2268.01</v>
       </c>
       <c r="I24" s="16">
         <f>IF(G24=0,0,H24/G24*100)</f>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="K24" s="17">
         <f>MAX(F24-H24,0)</f>
-        <v>1932.0</v>
+        <v>1931.99</v>
       </c>
       <c r="L24" s="17">
         <f>K24/4</f>
@@ -8193,11 +8193,11 @@
         <v>1.7</v>
       </c>
       <c r="O24" s="18">
-        <f>H24*44</f>
+        <f>H24*44.0</f>
         <v>99792</v>
       </c>
       <c r="P24" s="18">
-        <f>K24*44</f>
+        <f>K24*44.0</f>
         <v>85008</v>
       </c>
       <c r="Q24" s="31" t="str">
@@ -8229,11 +8229,11 @@
       </c>
       <c r="H25" s="17">
         <f>SUM('INPUT REALISASI'!E26:L26)</f>
-        <v>95.04</v>
+        <v>95.03</v>
       </c>
       <c r="I25" s="16">
         <f>IF(G25=0,0,H25/G25*100)</f>
-        <v>55.0</v>
+        <v>54.99</v>
       </c>
       <c r="J25" s="16">
         <f>IF(F25=0,0,H25/F25*100)</f>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="K25" s="17">
         <f>MAX(F25-H25,0)</f>
-        <v>224.96</v>
+        <v>224.97</v>
       </c>
       <c r="L25" s="17">
         <f>K25/4</f>
@@ -8256,12 +8256,12 @@
         <v>4.73</v>
       </c>
       <c r="O25" s="18">
-        <f>H25*640</f>
-        <v>60826</v>
+        <f>H25*640.0</f>
+        <v>60819</v>
       </c>
       <c r="P25" s="18">
-        <f>K25*640</f>
-        <v>143974</v>
+        <f>K25*640.0</f>
+        <v>143981</v>
       </c>
       <c r="Q25" s="30" t="str">
         <f>IF(I25&gt;=100,"TERCAPAI",IF(I25&gt;=90,"WASPADA",IF(I25&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -8288,11 +8288,11 @@
         <v>1100</v>
       </c>
       <c r="G26" s="17">
-        <v>733.33</v>
+        <v>733.36</v>
       </c>
       <c r="H26" s="17">
         <f>SUM('INPUT REALISASI'!E27:L27)</f>
-        <v>689.33</v>
+        <v>689.34</v>
       </c>
       <c r="I26" s="16">
         <f>IF(G26=0,0,H26/G26*100)</f>
@@ -8304,11 +8304,11 @@
       </c>
       <c r="K26" s="17">
         <f>MAX(F26-H26,0)</f>
-        <v>410.67</v>
+        <v>410.66</v>
       </c>
       <c r="L26" s="17">
         <f>K26/4</f>
-        <v>102.67</v>
+        <v>102.66</v>
       </c>
       <c r="M26" s="17">
         <f>H26/8</f>
@@ -8319,12 +8319,12 @@
         <v>1.19</v>
       </c>
       <c r="O26" s="18">
-        <f>H26*118</f>
-        <v>81341</v>
+        <f>H26*118.0</f>
+        <v>81342</v>
       </c>
       <c r="P26" s="18">
-        <f>K26*118</f>
-        <v>48459</v>
+        <f>K26*118.0</f>
+        <v>48458</v>
       </c>
       <c r="Q26" s="32" t="str">
         <f>IF(I26&gt;=100,"TERCAPAI",IF(I26&gt;=90,"WASPADA",IF(I26&gt;=75,"TERLAMBAT","KRITIS")))</f>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="H27" s="17">
         <f>SUM('INPUT REALISASI'!E28:L28)</f>
-        <v>7760.0</v>
+        <v>7760.01</v>
       </c>
       <c r="I27" s="16">
         <f>IF(G27=0,0,H27/G27*100)</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="K27" s="17">
         <f>MAX(F27-H27,0)</f>
-        <v>4240.0</v>
+        <v>4239.99</v>
       </c>
       <c r="L27" s="17">
         <f>K27/4</f>
@@ -8382,11 +8382,11 @@
         <v>1.09</v>
       </c>
       <c r="O27" s="18">
-        <f>H27*12</f>
+        <f>H27*12.0</f>
         <v>93120</v>
       </c>
       <c r="P27" s="18">
-        <f>K27*12</f>
+        <f>K27*12.0</f>
         <v>50880</v>
       </c>
       <c r="Q27" s="32" t="str">
@@ -8445,11 +8445,11 @@
         <v>2.92</v>
       </c>
       <c r="O28" s="18">
-        <f>H28*890</f>
+        <f>H28*890.0</f>
         <v>76006</v>
       </c>
       <c r="P28" s="18">
-        <f>K28*890</f>
+        <f>K28*890.0</f>
         <v>110894</v>
       </c>
       <c r="Q28" s="30" t="str">
@@ -9641,7 +9641,7 @@
         <v>235580000</v>
       </c>
       <c r="H7" s="19">
-        <v>157272799</v>
+        <v>152161122</v>
       </c>
       <c r="I7" s="16">
         <f>IF(G7=0,0,H7/G7*100)</f>
@@ -9669,7 +9669,7 @@
         <v>212620000</v>
       </c>
       <c r="H8" s="19">
-        <v>146830016</v>
+        <v>142604234</v>
       </c>
       <c r="I8" s="16">
         <f>IF(G8=0,0,H8/G8*100)</f>
@@ -9697,7 +9697,7 @@
         <v>203350000</v>
       </c>
       <c r="H9" s="19">
-        <v>146213868</v>
+        <v>144337830</v>
       </c>
       <c r="I9" s="16">
         <f>IF(G9=0,0,H9/G9*100)</f>
@@ -9725,7 +9725,7 @@
         <v>202880000</v>
       </c>
       <c r="H10" s="19">
-        <v>147164561</v>
+        <v>147169152</v>
       </c>
       <c r="I10" s="16">
         <f>IF(G10=0,0,H10/G10*100)</f>
@@ -9753,7 +9753,7 @@
         <v>208250000</v>
       </c>
       <c r="H11" s="19">
-        <v>162229299</v>
+        <v>162226749</v>
       </c>
       <c r="I11" s="16">
         <f>IF(G11=0,0,H11/G11*100)</f>
@@ -9781,7 +9781,7 @@
         <v>187090000</v>
       </c>
       <c r="H12" s="19">
-        <v>155994221</v>
+        <v>155995642</v>
       </c>
       <c r="I12" s="16">
         <f>IF(G12=0,0,H12/G12*100)</f>
@@ -9809,7 +9809,7 @@
         <v>226660000</v>
       </c>
       <c r="H13" s="19">
-        <v>179179868</v>
+        <v>179174730</v>
       </c>
       <c r="I13" s="16">
         <f>IF(G13=0,0,H13/G13*100)</f>
@@ -9837,7 +9837,7 @@
         <v>200890000</v>
       </c>
       <c r="H14" s="19">
-        <v>175784980</v>
+        <v>175778749</v>
       </c>
       <c r="I14" s="16">
         <f>IF(G14=0,0,H14/G14*100)</f>
@@ -10177,16 +10177,16 @@
         <v>265</v>
       </c>
       <c r="G7" s="17">
-        <v>224.96</v>
+        <v>224.97</v>
       </c>
       <c r="H7" s="17">
         <v>56.24</v>
       </c>
       <c r="I7" s="18">
-        <v>35994</v>
+        <v>35995</v>
       </c>
       <c r="J7" s="37">
-        <v>210561975</v>
+        <v>210572212</v>
       </c>
       <c r="K7" s="34">
         <v>55</v>
@@ -10215,7 +10215,7 @@
         <v>268</v>
       </c>
       <c r="G8" s="17">
-        <v>1722.67</v>
+        <v>1722.68</v>
       </c>
       <c r="H8" s="17">
         <v>430.67</v>
@@ -10253,16 +10253,16 @@
         <v>271</v>
       </c>
       <c r="G9" s="17">
-        <v>7.82</v>
+        <v>7.84</v>
       </c>
       <c r="H9" s="17">
         <v>1.96</v>
       </c>
       <c r="I9" s="18">
-        <v>17400</v>
+        <v>17444</v>
       </c>
       <c r="J9" s="37">
-        <v>101787075</v>
+        <v>102047400</v>
       </c>
       <c r="K9" s="34">
         <v>36</v>
@@ -10291,16 +10291,16 @@
         <v>274</v>
       </c>
       <c r="G10" s="17">
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
       <c r="H10" s="17">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="18">
-        <v>20804</v>
+        <v>20769</v>
       </c>
       <c r="J10" s="37">
-        <v>121700475</v>
+        <v>121498650</v>
       </c>
       <c r="K10" s="34">
         <v>44</v>
@@ -10329,16 +10329,16 @@
         <v>276</v>
       </c>
       <c r="G11" s="17">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="H11" s="17">
         <v>1.08</v>
       </c>
       <c r="I11" s="18">
-        <v>22680</v>
+        <v>22628</v>
       </c>
       <c r="J11" s="37">
-        <v>132678000</v>
+        <v>132370875</v>
       </c>
       <c r="K11" s="34">
         <v>50</v>
@@ -10367,7 +10367,7 @@
         <v>279</v>
       </c>
       <c r="G12" s="17">
-        <v>1253.62</v>
+        <v>1253.63</v>
       </c>
       <c r="H12" s="17">
         <v>313.41</v>
@@ -10376,7 +10376,7 @@
         <v>22252</v>
       </c>
       <c r="J12" s="37">
-        <v>130172738</v>
+        <v>130174200</v>
       </c>
       <c r="K12" s="34">
         <v>63</v>
@@ -10443,7 +10443,7 @@
         <v>284</v>
       </c>
       <c r="G14" s="17">
-        <v>1296</v>
+        <v>1295.99</v>
       </c>
       <c r="H14" s="17">
         <v>324</v>
@@ -10452,7 +10452,7 @@
         <v>18792</v>
       </c>
       <c r="J14" s="37">
-        <v>109933200</v>
+        <v>109931738</v>
       </c>
       <c r="K14" s="34">
         <v>69</v>
@@ -10481,16 +10481,16 @@
         <v>286</v>
       </c>
       <c r="G15" s="17">
-        <v>8.24</v>
+        <v>8.25</v>
       </c>
       <c r="H15" s="17">
         <v>2.06</v>
       </c>
       <c r="I15" s="18">
-        <v>23690</v>
+        <v>23719</v>
       </c>
       <c r="J15" s="37">
-        <v>138586500</v>
+        <v>138754688</v>
       </c>
       <c r="K15" s="34">
         <v>58</v>
@@ -10519,16 +10519,16 @@
         <v>289</v>
       </c>
       <c r="G16" s="17">
-        <v>15.11</v>
+        <v>15.09</v>
       </c>
       <c r="H16" s="17">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="I16" s="18">
-        <v>23420</v>
+        <v>23390</v>
       </c>
       <c r="J16" s="37">
-        <v>137009925</v>
+        <v>136828575</v>
       </c>
       <c r="K16" s="34">
         <v>71</v>
@@ -10595,16 +10595,16 @@
         <v>295</v>
       </c>
       <c r="G18" s="17">
-        <v>52.8</v>
+        <v>52.79</v>
       </c>
       <c r="H18" s="17">
         <v>13.2</v>
       </c>
       <c r="I18" s="18">
-        <v>12540</v>
+        <v>12538</v>
       </c>
       <c r="J18" s="37">
-        <v>73359000</v>
+        <v>73344375</v>
       </c>
       <c r="K18" s="34">
         <v>106</v>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C35" s="18">
         <f>'WORK PLAN'!P29</f>
-        <v>1926903</v>
+        <v>1926702</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>103</v>
@@ -11181,7 +11181,7 @@
         <v>343</v>
       </c>
       <c r="C5" s="18">
-        <v>143974</v>
+        <v>143981</v>
       </c>
       <c r="F5" s="26" t="s">
         <v>354</v>
@@ -11267,7 +11267,7 @@
         <v>347</v>
       </c>
       <c r="C9" s="18">
-        <v>94760</v>
+        <v>94875</v>
       </c>
       <c r="J9" s="26" t="s">
         <v>363</v>
@@ -11281,7 +11281,7 @@
         <v>348</v>
       </c>
       <c r="C10" s="18">
-        <v>93682</v>
+        <v>93558</v>
       </c>
       <c r="J10" s="26" t="s">
         <v>364</v>
@@ -11295,7 +11295,7 @@
         <v>349</v>
       </c>
       <c r="C11" s="18">
-        <v>90720</v>
+        <v>90510</v>
       </c>
       <c r="J11" s="26" t="s">
         <v>365</v>
@@ -11309,7 +11309,7 @@
         <v>350</v>
       </c>
       <c r="C12" s="18">
-        <v>89007</v>
+        <v>89008</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>366</v>
